--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1325,6 +1325,1808 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128340276</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406067</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6855007</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128340262</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97356</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>406243</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6854541</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128340269</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>406394</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6854632</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128340277</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>406292</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6854903</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128340257</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>406109</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6854552</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128340270</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>406277</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6854765</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128340275</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>406048</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6855005</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128340260</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92657</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>406207</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6854693</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128340256</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>405930</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6854608</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128340261</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>406186</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6854762</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128340274</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>406045</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6854999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128340255</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>405923</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6854588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128340272</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>406129</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6854879</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128340271</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>406219</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6854829</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128340278</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>406172</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6855024</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128340259</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>406237</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6854626</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128340273</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>406111</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6854885</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>97356</v>
+        <v>97361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340260</v>
+        <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92657</v>
+        <v>92650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406207</v>
+        <v>405930</v>
       </c>
       <c r="R15" t="n">
-        <v>6854693</v>
+        <v>6854608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340256</v>
+        <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405930</v>
+        <v>406186</v>
       </c>
       <c r="R16" t="n">
-        <v>6854608</v>
+        <v>6854762</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340261</v>
+        <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>92662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406186</v>
+        <v>406207</v>
       </c>
       <c r="R17" t="n">
-        <v>6854762</v>
+        <v>6854693</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R18" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R19" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>97454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R8" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B9" t="n">
-        <v>97361</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R9" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R8" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>97454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R9" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128340269</v>
+        <v>128340277</v>
       </c>
       <c r="B10" t="n">
         <v>92742</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406394</v>
+        <v>406292</v>
       </c>
       <c r="R10" t="n">
-        <v>6854632</v>
+        <v>6854903</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128340277</v>
+        <v>128340269</v>
       </c>
       <c r="B11" t="n">
         <v>92742</v>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406292</v>
+        <v>406394</v>
       </c>
       <c r="R11" t="n">
-        <v>6854903</v>
+        <v>6854632</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340256</v>
+        <v>128340261</v>
       </c>
       <c r="B15" t="n">
         <v>92742</v>
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405930</v>
+        <v>406186</v>
       </c>
       <c r="R15" t="n">
-        <v>6854608</v>
+        <v>6854762</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340261</v>
+        <v>128340256</v>
       </c>
       <c r="B16" t="n">
         <v>92742</v>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406186</v>
+        <v>405930</v>
       </c>
       <c r="R16" t="n">
-        <v>6854762</v>
+        <v>6854608</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340261</v>
+        <v>128340256</v>
       </c>
       <c r="B15" t="n">
         <v>92742</v>
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406186</v>
+        <v>405930</v>
       </c>
       <c r="R15" t="n">
-        <v>6854762</v>
+        <v>6854608</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340256</v>
+        <v>128340261</v>
       </c>
       <c r="B16" t="n">
         <v>92742</v>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405930</v>
+        <v>406186</v>
       </c>
       <c r="R16" t="n">
-        <v>6854608</v>
+        <v>6854762</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>97454</v>
+        <v>97466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128340277</v>
+        <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406292</v>
+        <v>406394</v>
       </c>
       <c r="R10" t="n">
-        <v>6854903</v>
+        <v>6854632</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128340269</v>
+        <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406394</v>
+        <v>406292</v>
       </c>
       <c r="R11" t="n">
-        <v>6854632</v>
+        <v>6854903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>97466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R8" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B9" t="n">
-        <v>97466</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R9" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>97466</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R8" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>97468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R9" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340261</v>
+        <v>128340260</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406186</v>
+        <v>406207</v>
       </c>
       <c r="R16" t="n">
-        <v>6854762</v>
+        <v>6854693</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340260</v>
+        <v>128340261</v>
       </c>
       <c r="B17" t="n">
-        <v>92766</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406207</v>
+        <v>406186</v>
       </c>
       <c r="R17" t="n">
-        <v>6854693</v>
+        <v>6854762</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340260</v>
+        <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92768</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406207</v>
+        <v>406186</v>
       </c>
       <c r="R16" t="n">
-        <v>6854693</v>
+        <v>6854762</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340261</v>
+        <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406186</v>
+        <v>406207</v>
       </c>
       <c r="R17" t="n">
-        <v>6854762</v>
+        <v>6854693</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>97469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R8" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B9" t="n">
-        <v>97468</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R9" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>97469</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R8" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>97469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R9" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B18" t="n">
         <v>92757</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R18" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B19" t="n">
         <v>92757</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R19" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R18" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R19" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340261</v>
+        <v>128340260</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406186</v>
+        <v>406207</v>
       </c>
       <c r="R16" t="n">
-        <v>6854762</v>
+        <v>6854693</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340260</v>
+        <v>128340261</v>
       </c>
       <c r="B17" t="n">
-        <v>92796</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406207</v>
+        <v>406186</v>
       </c>
       <c r="R17" t="n">
-        <v>6854693</v>
+        <v>6854762</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B18" t="n">
         <v>92784</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R18" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B19" t="n">
         <v>92784</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R19" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>97496</v>
+        <v>97509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128340269</v>
+        <v>128340277</v>
       </c>
       <c r="B10" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406394</v>
+        <v>406292</v>
       </c>
       <c r="R10" t="n">
-        <v>6854632</v>
+        <v>6854903</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128340277</v>
+        <v>128340269</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406292</v>
+        <v>406394</v>
       </c>
       <c r="R11" t="n">
-        <v>6854903</v>
+        <v>6854632</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340260</v>
       </c>
       <c r="B16" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340261</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R18" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R19" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>97509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R8" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B9" t="n">
-        <v>97509</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R9" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128340277</v>
+        <v>128340269</v>
       </c>
       <c r="B10" t="n">
         <v>92794</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406292</v>
+        <v>406394</v>
       </c>
       <c r="R10" t="n">
-        <v>6854903</v>
+        <v>6854632</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1645,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128340269</v>
+        <v>128340277</v>
       </c>
       <c r="B11" t="n">
         <v>92794</v>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406394</v>
+        <v>406292</v>
       </c>
       <c r="R11" t="n">
-        <v>6854632</v>
+        <v>6854903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340260</v>
+        <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92806</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406207</v>
+        <v>406186</v>
       </c>
       <c r="R16" t="n">
-        <v>6854693</v>
+        <v>6854762</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128340261</v>
+        <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406186</v>
+        <v>406207</v>
       </c>
       <c r="R17" t="n">
-        <v>6854762</v>
+        <v>6854693</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B18" t="n">
         <v>92794</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R18" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B19" t="n">
         <v>92794</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R19" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340262</v>
+        <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>97509</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406243</v>
+        <v>406067</v>
       </c>
       <c r="R8" t="n">
-        <v>6854541</v>
+        <v>6855007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128340276</v>
+        <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>97509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406067</v>
+        <v>406243</v>
       </c>
       <c r="R9" t="n">
-        <v>6855007</v>
+        <v>6854541</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128340274</v>
+        <v>128340255</v>
       </c>
       <c r="B18" t="n">
         <v>92794</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406045</v>
+        <v>405923</v>
       </c>
       <c r="R18" t="n">
-        <v>6854999</v>
+        <v>6854588</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128340255</v>
+        <v>128340274</v>
       </c>
       <c r="B19" t="n">
         <v>92794</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405923</v>
+        <v>406045</v>
       </c>
       <c r="R19" t="n">
-        <v>6854588</v>
+        <v>6854999</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -1330,7 +1330,7 @@
         <v>128340276</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128340262</v>
       </c>
       <c r="B9" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>128340269</v>
       </c>
       <c r="B10" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128340277</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128340257</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128340270</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128340275</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128340256</v>
       </c>
       <c r="B15" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>128340261</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>128340260</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128340255</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128340274</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>128340272</v>
       </c>
       <c r="B20" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128340271</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128340278</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128340259</v>
       </c>
       <c r="B23" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128340273</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 41782-2025 artfynd.xlsx
+++ b/artfynd/A 41782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149976</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149978</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340256</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340257</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340269</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340271</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340274</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340276</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340277</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340278</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340260</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600597</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149977</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,8 +3216,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340262</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>